--- a/rules/CORE-000737/negative/01/data/CORE-000737-negative-01.xlsx
+++ b/rules/CORE-000737/negative/01/data/CORE-000737-negative-01.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,37 +619,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>["FDATCHSP"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ts.xpt</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>$FDAdesired_empty_tsparmcds</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>["SDTIGVER", "SDTMVER"]</t>
+          <t>["RANDQT"]</t>
         </is>
       </c>
     </row>

--- a/rules/CORE-000737/negative/01/data/CORE-000737-negative-01.xlsx
+++ b/rules/CORE-000737/negative/01/data/CORE-000737-negative-01.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,7 +619,37 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>["RANDQT"]</t>
+          <t>["FDATCHSP"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>$FDAdesired_empty_tsparmcds</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>["SDTIGVER", "SDTMVER"]</t>
         </is>
       </c>
     </row>
